--- a/results/nhanes__sex__routine-blood-tests/results.xlsx
+++ b/results/nhanes__sex__routine-blood-tests/results.xlsx
@@ -24,15 +24,15 @@
     <sheet name="select" sheetId="15" r:id="rId15"/>
     <sheet name="select_picks_summary" sheetId="16" r:id="rId16"/>
     <sheet name="pareto" sheetId="17" r:id="rId17"/>
-    <sheet name="external" sheetId="18" r:id="rId18"/>
-    <sheet name="shap_by_group" sheetId="19" r:id="rId19"/>
+    <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="371">
   <si>
     <t>Value</t>
   </si>
@@ -601,21 +601,33 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
     <t>0.750 ± 0.001</t>
   </si>
   <si>
+    <t>0.747 ± 0.002</t>
+  </si>
+  <si>
     <t>0.785 ± 0.004</t>
   </si>
   <si>
+    <t>0.748 ± 0.002</t>
+  </si>
+  <si>
     <t>0.784 ± 0.004</t>
   </si>
   <si>
@@ -625,24 +637,36 @@
     <t>0.777 ± 0.005</t>
   </si>
   <si>
+    <t>0.842 ± 0.002</t>
+  </si>
+  <si>
     <t>0.793 ± 0.003</t>
   </si>
   <si>
     <t>0.776 ± 0.009</t>
   </si>
   <si>
+    <t>0.774 ± 0.004</t>
+  </si>
+  <si>
     <t>0.779 ± 0.011</t>
   </si>
   <si>
     <t>0.735 ± 0.001</t>
   </si>
   <si>
+    <t>0.731 ± 0.001</t>
+  </si>
+  <si>
     <t>0.734 ± 0.003</t>
   </si>
   <si>
     <t>0.726 ± 0.003</t>
   </si>
   <si>
+    <t>0.733 ± 0.001</t>
+  </si>
+  <si>
     <t>0.725 ± 0.003</t>
   </si>
   <si>
@@ -652,12 +676,18 @@
     <t>0.737 ± 0.006</t>
   </si>
   <si>
+    <t>0.697 ± 0.003</t>
+  </si>
+  <si>
     <t>0.732 ± 0.005</t>
   </si>
   <si>
     <t>0.726 ± 0.002</t>
   </si>
   <si>
+    <t>0.734 ± 0.006</t>
+  </si>
+  <si>
     <t>0.727 ± 0.003</t>
   </si>
   <si>
@@ -667,6 +697,9 @@
     <t>0.710 ± 0.002</t>
   </si>
   <si>
+    <t>0.704 ± 0.003</t>
+  </si>
+  <si>
     <t>0.708 ± 0.004</t>
   </si>
   <si>
@@ -682,24 +715,36 @@
     <t>0.674 ± 0.009</t>
   </si>
   <si>
+    <t>0.468 ± 0.008</t>
+  </si>
+  <si>
     <t>0.634 ± 0.008</t>
   </si>
   <si>
     <t>0.646 ± 0.010</t>
   </si>
   <si>
+    <t>0.671 ± 0.010</t>
+  </si>
+  <si>
     <t>0.645 ± 0.019</t>
   </si>
   <si>
     <t>0.514 ± 0.001</t>
   </si>
   <si>
+    <t>0.508 ± 0.001</t>
+  </si>
+  <si>
     <t>0.512 ± 0.003</t>
   </si>
   <si>
     <t>0.521 ± 0.003</t>
   </si>
   <si>
+    <t>0.510 ± 0.001</t>
+  </si>
+  <si>
     <t>0.520 ± 0.004</t>
   </si>
   <si>
@@ -709,48 +754,72 @@
     <t>0.528 ± 0.008</t>
   </si>
   <si>
+    <t>0.523 ± 0.006</t>
+  </si>
+  <si>
     <t>0.532 ± 0.006</t>
   </si>
   <si>
     <t>0.517 ± 0.007</t>
   </si>
   <si>
+    <t>0.524 ± 0.008</t>
+  </si>
+  <si>
     <t>0.520 ± 0.007</t>
   </si>
   <si>
     <t>0.053 ± 0.003</t>
   </si>
   <si>
+    <t>0.004 ± 0.004</t>
+  </si>
+  <si>
     <t>0.007 ± 0.008</t>
   </si>
   <si>
     <t>0.008 ± 0.005</t>
   </si>
   <si>
+    <t>0.013 ± 0.004</t>
+  </si>
+  <si>
     <t>0.007 ± 0.005</t>
   </si>
   <si>
     <t>0.047 ± 0.005</t>
   </si>
   <si>
+    <t>0.020 ± 0.004</t>
+  </si>
+  <si>
     <t>0.009 ± 0.007</t>
   </si>
   <si>
     <t>0.005 ± 0.002</t>
   </si>
   <si>
+    <t>0.014 ± 0.008</t>
+  </si>
+  <si>
     <t>0.850 ± 0.008</t>
   </si>
   <si>
     <t>0.972 ± 0.010</t>
   </si>
   <si>
+    <t>0.989 ± 0.013</t>
+  </si>
+  <si>
     <t>0.978 ± 0.024</t>
   </si>
   <si>
     <t>0.970 ± 0.018</t>
   </si>
   <si>
+    <t>0.962 ± 0.010</t>
+  </si>
+  <si>
     <t>0.974 ± 0.017</t>
   </si>
   <si>
@@ -760,12 +829,18 @@
     <t>0.882 ± 0.012</t>
   </si>
   <si>
+    <t>0.873 ± 0.023</t>
+  </si>
+  <si>
     <t>0.968 ± 0.027</t>
   </si>
   <si>
     <t>0.981 ± 0.008</t>
   </si>
   <si>
+    <t>0.953 ± 0.026</t>
+  </si>
+  <si>
     <t>0.978 ± 0.007</t>
   </si>
   <si>
@@ -775,18 +850,27 @@
     <t>0.045 ± 0.003</t>
   </si>
   <si>
+    <t>0.029 ± 0.008</t>
+  </si>
+  <si>
     <t>0.032 ± 0.013</t>
   </si>
   <si>
     <t>0.011 ± 0.006</t>
   </si>
   <si>
+    <t>0.024 ± 0.005</t>
+  </si>
+  <si>
     <t>0.083 ± 0.008</t>
   </si>
   <si>
     <t>0.068 ± 0.011</t>
   </si>
   <si>
+    <t>0.046 ± 0.016</t>
+  </si>
+  <si>
     <t>0.022 ± 0.012</t>
   </si>
   <si>
@@ -802,9 +886,15 @@
     <t>0.011 ± 0.005</t>
   </si>
   <si>
+    <t>0.027 ± 0.003</t>
+  </si>
+  <si>
     <t>0.026 ± 0.004</t>
   </si>
   <si>
+    <t>0.025 ± 0.007</t>
+  </si>
+  <si>
     <t>0.012 ± 0.008</t>
   </si>
   <si>
@@ -814,21 +904,33 @@
     <t>0.025 ± 0.004</t>
   </si>
   <si>
+    <t>0.031 ± 0.004</t>
+  </si>
+  <si>
     <t>0.035 ± 0.005</t>
   </si>
   <si>
     <t>0.012 ± 0.010</t>
   </si>
   <si>
+    <t>0.040 ± 0.003</t>
+  </si>
+  <si>
     <t>0.011 ± 0.008</t>
   </si>
   <si>
+    <t>0.010 ± 0.014</t>
+  </si>
+  <si>
     <t>0.025 ± 0.014</t>
   </si>
   <si>
     <t>0.023 ± 0.015</t>
   </si>
   <si>
+    <t>0.041 ± 0.010</t>
+  </si>
+  <si>
     <t>0.016 ± 0.014</t>
   </si>
   <si>
@@ -838,6 +940,9 @@
     <t>0.010 ± 0.003</t>
   </si>
   <si>
+    <t>0.016 ± 0.004</t>
+  </si>
+  <si>
     <t>0.019 ± 0.005</t>
   </si>
   <si>
@@ -853,6 +958,9 @@
     <t>0.009 ± 0.009</t>
   </si>
   <si>
+    <t>0.021 ± 0.007</t>
+  </si>
+  <si>
     <t>0.008 ± 0.006</t>
   </si>
   <si>
@@ -880,12 +988,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -895,12 +1009,18 @@
     <t>[-0.013, 0.005]</t>
   </si>
   <si>
+    <t>[-0.046, 0.027]</t>
+  </si>
+  <si>
     <t>[-0.047, 0.029]</t>
   </si>
   <si>
     <t>[-0.065, 0.033]</t>
   </si>
   <si>
+    <t>[-0.035, 0.026]</t>
+  </si>
+  <si>
     <t>[-0.065, 0.032]</t>
   </si>
   <si>
@@ -910,12 +1030,18 @@
     <t>[-0.026, 0.030]</t>
   </si>
   <si>
+    <t>[-0.062, 0.038]</t>
+  </si>
+  <si>
     <t>[-0.083, -0.007]</t>
   </si>
   <si>
     <t>[-0.079, -0.004]</t>
   </si>
   <si>
+    <t>[-0.087, 0.013]</t>
+  </si>
+  <si>
     <t>[-0.100, 0.015]</t>
   </si>
   <si>
@@ -925,12 +1051,18 @@
     <t>[-0.003, 0.001]</t>
   </si>
   <si>
+    <t>[-0.011, 0.001]</t>
+  </si>
+  <si>
     <t>[-0.009, 0.001]</t>
   </si>
   <si>
     <t>[-0.019, -0.000]</t>
   </si>
   <si>
+    <t>[-0.007, 0.001]</t>
+  </si>
+  <si>
     <t>[-0.019, -0.001]</t>
   </si>
   <si>
@@ -940,12 +1072,18 @@
     <t>[-0.005, 0.009]</t>
   </si>
   <si>
+    <t>[-0.052, -0.024]</t>
+  </si>
+  <si>
     <t>[-0.015, 0.005]</t>
   </si>
   <si>
     <t>[-0.017, -0.001]</t>
   </si>
   <si>
+    <t>[-0.008, 0.005]</t>
+  </si>
+  <si>
     <t>[-0.018, 0.001]</t>
   </si>
   <si>
@@ -970,33 +1108,27 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.779 ± 0.017</t>
+    <t>0.774 ± 0.011</t>
   </si>
   <si>
     <t>0.763 ± 0.001</t>
   </si>
   <si>
-    <t>0.727 ± 0.004</t>
-  </si>
-  <si>
     <t>0.734 ± 0.004</t>
   </si>
   <si>
-    <t>0.644 ± 0.018</t>
+    <t>0.649 ± 0.011</t>
   </si>
   <si>
     <t>0.688 ± 0.012</t>
   </si>
   <si>
-    <t>0.031 ± 0.021</t>
+    <t>0.028 ± 0.016</t>
   </si>
   <si>
     <t>0.044 ± 0.002</t>
   </si>
   <si>
-    <t>0.012 ± 0.015</t>
-  </si>
-  <si>
     <t>0.028 ± 0.002</t>
   </si>
   <si>
@@ -1007,6 +1139,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -2244,7 +2382,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2328,34 +2466,34 @@
         <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F3" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G3" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="H3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="I3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="J3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="K3" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="L3" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2369,7 +2507,7 @@
         <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
         <v>96</v>
@@ -2378,19 +2516,19 @@
         <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="I4" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="J4" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="K4" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="L4" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2398,34 +2536,34 @@
         <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="H5" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="I5" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="J5" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K5" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="L5" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2433,34 +2571,34 @@
         <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F6" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G6" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="I6" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="J6" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="K6" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="L6" t="s">
-        <v>156</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2468,253 +2606,393 @@
         <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I7" t="s">
+        <v>274</v>
+      </c>
+      <c r="J7" t="s">
+        <v>283</v>
+      </c>
+      <c r="K7" t="s">
+        <v>292</v>
+      </c>
+      <c r="L7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" t="s">
         <v>222</v>
       </c>
-      <c r="G7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I7" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" t="s">
-        <v>255</v>
-      </c>
-      <c r="K7" t="s">
-        <v>262</v>
-      </c>
-      <c r="L7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" t="s">
-        <v>95</v>
-      </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="G8" t="s">
-        <v>128</v>
+        <v>249</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="I8" t="s">
-        <v>144</v>
+        <v>275</v>
       </c>
       <c r="J8" t="s">
-        <v>144</v>
+        <v>284</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="L8" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F9" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G9" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="H9" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="I9" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="J9" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="K9" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="L9" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="G10" t="s">
         <v>128</v>
       </c>
       <c r="H10" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="J10" t="s">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="K10" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="L10" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F11" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G11" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="H11" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="I11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="K11" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="L11" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="G12" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="I12" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="J12" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="K12" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="L12" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E13" t="s">
+        <v>227</v>
+      </c>
+      <c r="F13" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" t="s">
+        <v>278</v>
+      </c>
+      <c r="J13" t="s">
+        <v>278</v>
+      </c>
+      <c r="K13" t="s">
+        <v>295</v>
+      </c>
+      <c r="L13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F14" t="s">
+        <v>241</v>
+      </c>
+      <c r="G14" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" t="s">
+        <v>266</v>
+      </c>
+      <c r="I14" t="s">
+        <v>279</v>
+      </c>
+      <c r="J14" t="s">
+        <v>285</v>
+      </c>
+      <c r="K14" t="s">
+        <v>296</v>
+      </c>
+      <c r="L14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
         <v>191</v>
       </c>
-      <c r="C13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" t="s">
+        <v>242</v>
+      </c>
+      <c r="G15" t="s">
+        <v>254</v>
+      </c>
+      <c r="H15" t="s">
+        <v>267</v>
+      </c>
+      <c r="I15" t="s">
+        <v>280</v>
+      </c>
+      <c r="J15" t="s">
+        <v>280</v>
+      </c>
+      <c r="K15" t="s">
+        <v>297</v>
+      </c>
+      <c r="L15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" t="s">
+        <v>255</v>
+      </c>
+      <c r="H16" t="s">
+        <v>268</v>
+      </c>
+      <c r="I16" t="s">
+        <v>249</v>
+      </c>
+      <c r="J16" t="s">
+        <v>286</v>
+      </c>
+      <c r="K16" t="s">
+        <v>298</v>
+      </c>
+      <c r="L16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" t="s">
         <v>218</v>
       </c>
-      <c r="F13" t="s">
-        <v>227</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="E17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" t="s">
         <v>156</v>
       </c>
-      <c r="H13" t="s">
-        <v>244</v>
-      </c>
-      <c r="I13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J13" t="s">
-        <v>257</v>
-      </c>
-      <c r="K13" t="s">
-        <v>265</v>
-      </c>
-      <c r="L13" t="s">
-        <v>273</v>
+      <c r="H17" t="s">
+        <v>269</v>
+      </c>
+      <c r="I17" t="s">
+        <v>281</v>
+      </c>
+      <c r="J17" t="s">
+        <v>287</v>
+      </c>
+      <c r="K17" t="s">
+        <v>299</v>
+      </c>
+      <c r="L17" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2722,7 +3000,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2804,16 +3082,16 @@
         <v>189</v>
       </c>
       <c r="C5">
-        <v>0.6919999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5">
         <v>0.249</v>
       </c>
       <c r="E5">
-        <v>0.724</v>
+        <v>0.719</v>
       </c>
       <c r="F5">
-        <v>0.232</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2821,16 +3099,16 @@
         <v>190</v>
       </c>
       <c r="C6">
-        <v>0.634</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D6">
-        <v>0.182</v>
+        <v>0.249</v>
       </c>
       <c r="E6">
-        <v>0.628</v>
+        <v>0.724</v>
       </c>
       <c r="F6">
-        <v>0.178</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2838,67 +3116,67 @@
         <v>191</v>
       </c>
       <c r="C7">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="D7">
         <v>0.182</v>
       </c>
       <c r="E7">
-        <v>0.627</v>
+        <v>0.628</v>
       </c>
       <c r="F7">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C8">
-        <v>0.636</v>
+        <v>0.696</v>
       </c>
       <c r="D8">
-        <v>0.187</v>
+        <v>0.255</v>
       </c>
       <c r="E8">
-        <v>0.705</v>
+        <v>0.721</v>
       </c>
       <c r="F8">
-        <v>0.213</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C9">
-        <v>0.633</v>
+        <v>0.632</v>
       </c>
       <c r="D9">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="E9">
-        <v>0.717</v>
+        <v>0.627</v>
       </c>
       <c r="F9">
-        <v>0.22</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10">
-        <v>0.641</v>
+        <v>0.636</v>
       </c>
       <c r="D10">
         <v>0.187</v>
       </c>
       <c r="E10">
-        <v>0.708</v>
+        <v>0.705</v>
       </c>
       <c r="F10">
         <v>0.213</v>
@@ -2906,59 +3184,127 @@
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11">
-        <v>0.623</v>
+        <v>0.633</v>
       </c>
       <c r="D11">
-        <v>0.173</v>
+        <v>0.184</v>
       </c>
       <c r="E11">
-        <v>0.645</v>
+        <v>0.717</v>
       </c>
       <c r="F11">
-        <v>0.167</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C12">
-        <v>0.637</v>
+        <v>0.641</v>
       </c>
       <c r="D12">
-        <v>0.198</v>
+        <v>0.187</v>
       </c>
       <c r="E12">
-        <v>0.655</v>
+        <v>0.708</v>
       </c>
       <c r="F12">
-        <v>0.191</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13">
+        <v>0.446</v>
+      </c>
+      <c r="D13">
+        <v>0.068</v>
+      </c>
+      <c r="E13">
+        <v>0.492</v>
+      </c>
+      <c r="F13">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14">
+        <v>0.623</v>
+      </c>
+      <c r="D14">
+        <v>0.173</v>
+      </c>
+      <c r="E14">
+        <v>0.645</v>
+      </c>
+      <c r="F14">
+        <v>0.167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
         <v>191</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.637</v>
+      </c>
+      <c r="D15">
+        <v>0.198</v>
+      </c>
+      <c r="E15">
+        <v>0.655</v>
+      </c>
+      <c r="F15">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16">
+        <v>0.665</v>
+      </c>
+      <c r="D16">
+        <v>0.214</v>
+      </c>
+      <c r="E16">
+        <v>0.678</v>
+      </c>
+      <c r="F16">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17">
         <v>0.64</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.192</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.649</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.189</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2966,7 +3312,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2977,22 +3323,22 @@
         <v>185</v>
       </c>
       <c r="D1" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="E1" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="F1" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="G1" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="H1" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="I1" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3003,13 +3349,13 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="D2">
         <v>0.045</v>
       </c>
       <c r="E2" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="F2">
         <v>0.004</v>
@@ -3018,7 +3364,7 @@
         <v>-0.001</v>
       </c>
       <c r="H2" t="s">
-        <v>295</v>
+        <v>337</v>
       </c>
       <c r="I2">
         <v>0.848</v>
@@ -3032,13 +3378,13 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="D3">
         <v>-0.006</v>
       </c>
       <c r="E3" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="F3">
         <v>0.222</v>
@@ -3047,7 +3393,7 @@
         <v>-0.001</v>
       </c>
       <c r="H3" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="I3">
         <v>0.62</v>
@@ -3061,25 +3407,25 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="D4">
-        <v>-0.018</v>
+        <v>-0.016</v>
       </c>
       <c r="E4" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="F4">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="G4">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="H4" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
       <c r="I4">
-        <v>0.164</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3090,25 +3436,25 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="D5">
-        <v>-0.023</v>
+        <v>-0.018</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="F5">
-        <v>0.298</v>
+        <v>0.38</v>
       </c>
       <c r="G5">
-        <v>-0.008999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="H5" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="I5">
-        <v>0.046</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3119,25 +3465,25 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="D6">
         <v>-0.023</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="F6">
-        <v>0.276</v>
+        <v>0.298</v>
       </c>
       <c r="G6">
         <v>-0.008999999999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="I6">
-        <v>0.036</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3145,28 +3491,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="D7">
-        <v>0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="F7">
-        <v>0.372</v>
+        <v>0.392</v>
       </c>
       <c r="G7">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="H7" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="I7">
-        <v>0.73</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3174,28 +3520,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="D8">
-        <v>0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="F8">
-        <v>0.97</v>
+        <v>0.276</v>
       </c>
       <c r="G8">
-        <v>0.002</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H8" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="I8">
-        <v>0.5600000000000001</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3206,25 +3552,25 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="D9">
-        <v>-0.048</v>
+        <v>0.012</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="F9">
-        <v>0.032</v>
+        <v>0.372</v>
       </c>
       <c r="G9">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="I9">
-        <v>0.312</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3235,25 +3581,25 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="D10">
-        <v>-0.047</v>
+        <v>0.001</v>
       </c>
       <c r="E10" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="F10">
-        <v>0.04</v>
+        <v>0.97</v>
       </c>
       <c r="G10">
-        <v>-0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="I10">
-        <v>0.032</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3264,24 +3610,140 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="D11">
+        <v>-0.016</v>
+      </c>
+      <c r="E11" t="s">
+        <v>332</v>
+      </c>
+      <c r="F11">
+        <v>0.512</v>
+      </c>
+      <c r="G11">
+        <v>-0.037</v>
+      </c>
+      <c r="H11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12">
+        <v>-0.048</v>
+      </c>
+      <c r="E12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F12">
+        <v>0.032</v>
+      </c>
+      <c r="G12">
+        <v>-0.005</v>
+      </c>
+      <c r="H12" t="s">
+        <v>347</v>
+      </c>
+      <c r="I12">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13">
+        <v>-0.047</v>
+      </c>
+      <c r="E13" t="s">
+        <v>334</v>
+      </c>
+      <c r="F13">
+        <v>0.04</v>
+      </c>
+      <c r="G13">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="H13" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D14">
+        <v>-0.047</v>
+      </c>
+      <c r="E14" t="s">
+        <v>335</v>
+      </c>
+      <c r="F14">
+        <v>0.11</v>
+      </c>
+      <c r="G14">
+        <v>-0.002</v>
+      </c>
+      <c r="H14" t="s">
+        <v>349</v>
+      </c>
+      <c r="I14">
+        <v>0.632</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15">
         <v>-0.056</v>
       </c>
-      <c r="E11" t="s">
-        <v>294</v>
-      </c>
-      <c r="F11">
+      <c r="E15" t="s">
+        <v>336</v>
+      </c>
+      <c r="F15">
         <v>0.108</v>
       </c>
-      <c r="G11">
+      <c r="G15">
         <v>-0.008</v>
       </c>
-      <c r="H11" t="s">
-        <v>304</v>
-      </c>
-      <c r="I11">
+      <c r="H15" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15">
         <v>0.094</v>
       </c>
     </row>
@@ -3297,13 +3759,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="C1" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="D1" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="E1" t="s">
         <v>169</v>
@@ -3312,10 +3774,10 @@
         <v>185</v>
       </c>
       <c r="G1" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="H1" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3329,13 +3791,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E2" t="s">
         <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="G2">
         <v>0.709</v>
@@ -3355,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E3" t="s">
         <v>74</v>
@@ -3381,13 +3843,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E4" t="s">
         <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="G4">
         <v>0.724</v>
@@ -3407,7 +3869,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E5" t="s">
         <v>74</v>
@@ -3433,13 +3895,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G6">
         <v>0.725</v>
@@ -3459,7 +3921,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
@@ -3485,13 +3947,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G8">
         <v>0.733</v>
@@ -3511,7 +3973,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
@@ -3537,19 +3999,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E10" t="s">
         <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="G10">
-        <v>0.711</v>
+        <v>0.721</v>
       </c>
       <c r="H10">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3563,7 +4025,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
@@ -3589,13 +4051,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G12">
         <v>0.724</v>
@@ -3615,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
@@ -3641,13 +4103,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="G14">
         <v>0.722</v>
@@ -3667,7 +4129,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
@@ -3693,13 +4155,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="G16">
         <v>0.725</v>
@@ -3719,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E17" t="s">
         <v>74</v>
@@ -3745,13 +4207,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G18">
         <v>0.724</v>
@@ -3771,7 +4233,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
@@ -3797,13 +4259,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E20" t="s">
         <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G20">
         <v>0.719</v>
@@ -3823,7 +4285,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="E21" t="s">
         <v>74</v>
@@ -3850,7 +4312,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="B1" t="s">
         <v>62</v>
@@ -3873,48 +4335,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="E2" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="F2" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="G2" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="D3" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="E3" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="F3" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="G3" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3924,7 +4386,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3935,7 +4397,7 @@
         <v>185</v>
       </c>
       <c r="D1" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3946,7 +4408,7 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3960,7 +4422,7 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -3974,7 +4436,7 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -3988,7 +4450,7 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -4002,10 +4464,24 @@
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4491,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4032,7 +4508,7 @@
         <v>118</v>
       </c>
       <c r="E1" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4085,13 +4561,13 @@
         <v>189</v>
       </c>
       <c r="C5">
-        <v>0.734</v>
+        <v>0.731</v>
       </c>
       <c r="D5">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4099,13 +4575,13 @@
         <v>190</v>
       </c>
       <c r="C6">
-        <v>0.726</v>
+        <v>0.734</v>
       </c>
       <c r="D6">
-        <v>0.011</v>
+        <v>0.036</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4113,27 +4589,24 @@
         <v>191</v>
       </c>
       <c r="C7">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="D7">
         <v>0.011</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C8">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="D8">
-        <v>0.06900000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -4141,78 +4614,137 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C9">
-        <v>0.736</v>
+        <v>0.725</v>
       </c>
       <c r="D9">
-        <v>0.083</v>
+        <v>0.011</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10">
-        <v>0.737</v>
+        <v>0.735</v>
       </c>
       <c r="D10">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11">
-        <v>0.732</v>
+        <v>0.736</v>
       </c>
       <c r="D11">
-        <v>0.026</v>
+        <v>0.083</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C12">
-        <v>0.726</v>
+        <v>0.737</v>
       </c>
       <c r="D12">
-        <v>0.018</v>
+        <v>0.068</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13">
+        <v>0.697</v>
+      </c>
+      <c r="D13">
+        <v>0.046</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14">
+        <v>0.732</v>
+      </c>
+      <c r="D14">
+        <v>0.026</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>191</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.726</v>
+      </c>
+      <c r="D15">
+        <v>0.018</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16">
+        <v>0.734</v>
+      </c>
+      <c r="D16">
+        <v>0.025</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17">
         <v>0.727</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.012</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E17" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4220,377 +4752,256 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:4">
       <c r="B1" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <v>0.4891000092029572</v>
+      </c>
+      <c r="C2">
+        <v>0.5131000280380249</v>
+      </c>
+      <c r="D2">
+        <v>0.5005999803543091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>0.413100004196167</v>
+      </c>
+      <c r="C3">
+        <v>0.3998000025749207</v>
+      </c>
+      <c r="D3">
+        <v>0.4066999852657318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>0.2364999949932098</v>
+      </c>
+      <c r="C4">
+        <v>0.2433999925851822</v>
+      </c>
+      <c r="D4">
+        <v>0.2398000061511993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>0.25</v>
+      </c>
+      <c r="C5">
+        <v>0.221900001168251</v>
+      </c>
+      <c r="D5">
+        <v>0.2364999949932098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>0.1635999977588654</v>
+      </c>
+      <c r="C6">
+        <v>0.1940000057220459</v>
+      </c>
+      <c r="D6">
+        <v>0.1782000064849854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>0.1571999937295914</v>
+      </c>
+      <c r="C7">
+        <v>0.1840000003576279</v>
+      </c>
+      <c r="D7">
+        <v>0.1701000034809113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>0.128600001335144</v>
+      </c>
+      <c r="C8">
+        <v>0.120899997651577</v>
+      </c>
+      <c r="D8">
+        <v>0.1248999983072281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9">
+        <v>0.1042999997735023</v>
+      </c>
+      <c r="C9">
+        <v>0.1465000063180923</v>
+      </c>
+      <c r="D9">
+        <v>0.124600000679493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10">
+        <v>0.133200004696846</v>
+      </c>
+      <c r="C10">
+        <v>0.1093999966979027</v>
+      </c>
+      <c r="D10">
+        <v>0.1216999962925911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>0.1042999997735023</v>
+      </c>
+      <c r="C11">
+        <v>0.120899997651577</v>
+      </c>
+      <c r="D11">
+        <v>0.1123000010848045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0.08860000222921371</v>
+      </c>
+      <c r="C12">
+        <v>0.09300000220537186</v>
+      </c>
+      <c r="D12">
+        <v>0.09070000052452087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>0.06530000269412994</v>
+      </c>
+      <c r="C13">
+        <v>0.1172000020742416</v>
+      </c>
+      <c r="D13">
+        <v>0.09030000120401382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0.06750000268220901</v>
+      </c>
+      <c r="C14">
+        <v>0.0828000009059906</v>
+      </c>
+      <c r="D14">
+        <v>0.07490000128746033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>0.05930000171065331</v>
+      </c>
+      <c r="C15">
+        <v>0.07320000231266022</v>
+      </c>
+      <c r="D15">
+        <v>0.06599999964237213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>0.05249999836087227</v>
+      </c>
+      <c r="C16">
+        <v>0.05840000137686729</v>
+      </c>
+      <c r="D16">
+        <v>0.05539999902248383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17">
+        <v>0.02859999984502792</v>
+      </c>
+      <c r="C17">
+        <v>0.02850000001490116</v>
+      </c>
+      <c r="D17">
+        <v>0.02859999984502792</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D2">
-        <v>0.784</v>
-      </c>
-      <c r="E2">
-        <v>0.749</v>
-      </c>
-      <c r="F2">
-        <v>0.696</v>
-      </c>
-      <c r="G2">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H2">
-        <v>0.033</v>
-      </c>
-      <c r="I2">
-        <v>0.033</v>
-      </c>
-      <c r="J2">
-        <v>0.681</v>
-      </c>
-      <c r="K2">
-        <v>0.714</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D3">
-        <v>0.783</v>
-      </c>
-      <c r="E3">
-        <v>0.748</v>
-      </c>
-      <c r="F3">
-        <v>0.696</v>
-      </c>
-      <c r="G3">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H3">
-        <v>0.019</v>
-      </c>
-      <c r="I3">
-        <v>0.031</v>
-      </c>
-      <c r="J3">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="K3">
-        <v>0.707</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D4">
-        <v>0.773</v>
-      </c>
-      <c r="E4">
-        <v>0.746</v>
-      </c>
-      <c r="F4">
-        <v>0.705</v>
-      </c>
-      <c r="G4">
-        <v>0.746</v>
-      </c>
-      <c r="H4">
-        <v>0.013</v>
-      </c>
-      <c r="I4">
-        <v>0.032</v>
-      </c>
-      <c r="J4">
-        <v>0.698</v>
-      </c>
-      <c r="K4">
-        <v>0.711</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D5">
-        <v>0.827</v>
-      </c>
-      <c r="E5">
-        <v>0.724</v>
-      </c>
-      <c r="F5">
-        <v>0.571</v>
-      </c>
-      <c r="H5">
-        <v>0.003</v>
-      </c>
-      <c r="I5">
-        <v>0.017</v>
-      </c>
-      <c r="J5">
-        <v>0.573</v>
-      </c>
-      <c r="K5">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D6">
-        <v>0.827</v>
-      </c>
-      <c r="E6">
-        <v>0.727</v>
-      </c>
-      <c r="F6">
-        <v>0.578</v>
-      </c>
-      <c r="H6">
-        <v>0.002</v>
-      </c>
-      <c r="I6">
-        <v>0.016</v>
-      </c>
-      <c r="J6">
-        <v>0.577</v>
-      </c>
-      <c r="K6">
-        <v>0.579</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7">
-        <v>0.791</v>
-      </c>
-      <c r="E7">
-        <v>0.74</v>
-      </c>
-      <c r="F7">
-        <v>0.666</v>
-      </c>
-      <c r="G7">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.007</v>
-      </c>
-      <c r="I7">
-        <v>0.021</v>
-      </c>
-      <c r="J7">
-        <v>0.663</v>
-      </c>
-      <c r="K7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8">
-        <v>0.79</v>
-      </c>
-      <c r="E8">
-        <v>0.74</v>
-      </c>
-      <c r="F8">
-        <v>0.666</v>
-      </c>
-      <c r="G8">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="H8">
-        <v>0.012</v>
-      </c>
-      <c r="I8">
-        <v>0.017</v>
-      </c>
-      <c r="J8">
-        <v>0.661</v>
-      </c>
-      <c r="K8">
-        <v>0.672</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D9">
-        <v>0.804</v>
-      </c>
-      <c r="E9">
-        <v>0.728</v>
-      </c>
-      <c r="F9">
-        <v>0.615</v>
-      </c>
-      <c r="G9">
-        <v>0.751</v>
-      </c>
-      <c r="H9">
-        <v>0.142</v>
-      </c>
-      <c r="I9">
-        <v>0.142</v>
-      </c>
-      <c r="J9">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="K9">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10">
-        <v>0.8</v>
-      </c>
-      <c r="E10">
-        <v>0.728</v>
-      </c>
-      <c r="F10">
-        <v>0.622</v>
-      </c>
-      <c r="H10">
-        <v>0.053</v>
-      </c>
-      <c r="I10">
-        <v>0.053</v>
-      </c>
-      <c r="J10">
-        <v>0.648</v>
-      </c>
-      <c r="K10">
-        <v>0.594</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>284</v>
-      </c>
-      <c r="D11">
-        <v>0.786</v>
-      </c>
-      <c r="E11">
-        <v>0.735</v>
-      </c>
-      <c r="F11">
-        <v>0.658</v>
-      </c>
-      <c r="H11">
-        <v>0.029</v>
-      </c>
-      <c r="I11">
-        <v>0.029</v>
-      </c>
-      <c r="J11">
-        <v>0.672</v>
-      </c>
-      <c r="K11">
-        <v>0.643</v>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4600,256 +5011,63 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="D1" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>0.4891000092029572</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>0.5131000280380249</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0.5005999803543091</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>0.413100004196167</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>0.3998000025749207</v>
+        <v>2.88</v>
       </c>
       <c r="D3">
-        <v>0.4066999852657318</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>0.2364999949932098</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>0.2433999925851822</v>
+        <v>2.94</v>
       </c>
       <c r="D4">
-        <v>0.2398000061511993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5">
-        <v>0.25</v>
-      </c>
-      <c r="C5">
-        <v>0.221900001168251</v>
-      </c>
-      <c r="D5">
-        <v>0.2364999949932098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6">
-        <v>0.1635999977588654</v>
-      </c>
-      <c r="C6">
-        <v>0.1940000057220459</v>
-      </c>
-      <c r="D6">
-        <v>0.1782000064849854</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7">
-        <v>0.1571999937295914</v>
-      </c>
-      <c r="C7">
-        <v>0.1840000003576279</v>
-      </c>
-      <c r="D7">
-        <v>0.1701000034809113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8">
-        <v>0.128600001335144</v>
-      </c>
-      <c r="C8">
-        <v>0.120899997651577</v>
-      </c>
-      <c r="D8">
-        <v>0.1248999983072281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9">
-        <v>0.1042999997735023</v>
-      </c>
-      <c r="C9">
-        <v>0.1465000063180923</v>
-      </c>
-      <c r="D9">
-        <v>0.124600000679493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10">
-        <v>0.133200004696846</v>
-      </c>
-      <c r="C10">
-        <v>0.1093999966979027</v>
-      </c>
-      <c r="D10">
-        <v>0.1216999962925911</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11">
-        <v>0.1042999997735023</v>
-      </c>
-      <c r="C11">
-        <v>0.120899997651577</v>
-      </c>
-      <c r="D11">
-        <v>0.1123000010848045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12">
-        <v>0.08860000222921371</v>
-      </c>
-      <c r="C12">
-        <v>0.09300000220537186</v>
-      </c>
-      <c r="D12">
-        <v>0.09070000052452087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13">
-        <v>0.06530000269412994</v>
-      </c>
-      <c r="C13">
-        <v>0.1172000020742416</v>
-      </c>
-      <c r="D13">
-        <v>0.09030000120401382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14">
-        <v>0.06750000268220901</v>
-      </c>
-      <c r="C14">
-        <v>0.0828000009059906</v>
-      </c>
-      <c r="D14">
-        <v>0.07490000128746033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15">
-        <v>0.05930000171065331</v>
-      </c>
-      <c r="C15">
-        <v>0.07320000231266022</v>
-      </c>
-      <c r="D15">
-        <v>0.06599999964237213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>0.05249999836087227</v>
-      </c>
-      <c r="C16">
-        <v>0.05840000137686729</v>
-      </c>
-      <c r="D16">
-        <v>0.05539999902248383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17">
-        <v>0.02859999984502792</v>
-      </c>
-      <c r="C17">
-        <v>0.02850000001490116</v>
-      </c>
-      <c r="D17">
-        <v>0.02859999984502792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
